--- a/ml/personalization/training_dataset_sample.xlsx
+++ b/ml/personalization/training_dataset_sample.xlsx
@@ -4688,7 +4688,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Values are written verbatim from app/ml/features.py -- nothing on this sheet is rounded, scaled or recomputed. Cell display formats are cosmetic only; the stored value is the exact float the model receives. 'segment' is the target, not an input.</t>
+          <t>Values come straight from app/ml/features.py: nothing here is rounded, scaled or recomputed, and the display formats are cosmetic only. XLSX stores numbers as decimal text, so a stored value can differ from the in-memory float in its last binary digit (measured worst case across this sample: 5.4e-16 relative, ~2 ULP). 'segment' is the target, not an input feature.</t>
         </is>
       </c>
     </row>
